--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2428"/>
+  <dimension ref="A1:C2436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36876,6 +36876,134 @@
         <v>134</v>
       </c>
     </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rainville n 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2429" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2430" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="C2431" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="C2432" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="C2433" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="C2434" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc des princes
+  paris </t>
+        </is>
+      </c>
+      <c r="C2435" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="C2436" t="n">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2436"/>
+  <dimension ref="A1:C2444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37004,6 +37004,130 @@
         <v>135</v>
       </c>
     </row>
+    <row r="2437">
+      <c r="A2437" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2437" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2438" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2439" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2440" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2440" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B2441" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="C2441" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B2442" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="C2442" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B2443" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="C2443" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B2444" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="C2444" t="n">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2444"/>
+  <dimension ref="A1:C2446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37128,6 +37128,38 @@
         <v>260</v>
       </c>
     </row>
+    <row r="2445">
+      <c r="A2445" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2445" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2446" t="n">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2446"/>
+  <dimension ref="A1:C2449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37160,6 +37160,54 @@
         <v>105</v>
       </c>
     </row>
+    <row r="2447">
+      <c r="A2447" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2447" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2448" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2449" t="n">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2449"/>
+  <dimension ref="A1:C2450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37208,6 +37208,21 @@
         <v>107</v>
       </c>
     </row>
+    <row r="2450">
+      <c r="A2450" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B2450" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="C2450" t="n">
+        <v>314</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2450"/>
+  <dimension ref="A1:C2453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37223,6 +37223,51 @@
         <v>314</v>
       </c>
     </row>
+    <row r="2451">
+      <c r="A2451" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B2451" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="C2451" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B2452" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="C2452" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B2453" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="C2453" t="n">
+        <v>315</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2450"/>
+  <dimension ref="A1:C2421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36163,31 +36163,33 @@
     <row r="2383">
       <c r="A2383" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>referee</t>
         </is>
       </c>
       <c r="B2383" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t xml:space="preserve">pignard j 
+  fra </t>
         </is>
       </c>
       <c r="C2383" t="n">
-        <v>312</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2384">
       <c r="A2384" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>referee</t>
         </is>
       </c>
       <c r="B2384" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t xml:space="preserve">frappart s 
+  fra </t>
         </is>
       </c>
       <c r="C2384" t="n">
-        <v>258</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2385">
@@ -36198,7 +36200,7 @@
       </c>
       <c r="B2385" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
@@ -36214,7 +36216,7 @@
       </c>
       <c r="B2386" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
@@ -36230,7 +36232,7 @@
       </c>
       <c r="B2387" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
@@ -36246,476 +36248,492 @@
       </c>
       <c r="B2388" t="inlineStr">
         <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2388" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2389" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2390" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2391" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2392" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2393" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
           <t xml:space="preserve">pignard j 
   fra </t>
         </is>
       </c>
-      <c r="C2388" t="n">
+      <c r="C2394" t="n">
         <v>101</v>
       </c>
     </row>
-    <row r="2389">
-      <c r="A2389" t="inlineStr">
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
         <is>
           <t>referee</t>
         </is>
       </c>
-      <c r="B2389" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
-      <c r="C2389" t="n">
+      <c r="C2395" t="n">
         <v>101</v>
       </c>
     </row>
-    <row r="2390">
-      <c r="A2390" t="inlineStr">
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
         <is>
           <t>referee</t>
         </is>
       </c>
-      <c r="B2390" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e 
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
-      <c r="C2390" t="n">
+      <c r="C2396" t="n">
         <v>101</v>
       </c>
     </row>
-    <row r="2391">
-      <c r="A2391" t="inlineStr">
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
         <is>
           <t>referee</t>
         </is>
       </c>
-      <c r="B2391" t="inlineStr">
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2397" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2398" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2399" t="inlineStr">
         <is>
           <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
-      <c r="C2391" t="n">
+      <c r="C2399" t="n">
         <v>101</v>
       </c>
     </row>
-    <row r="2392">
-      <c r="A2392" t="inlineStr">
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
         <is>
           <t>referee</t>
         </is>
       </c>
-      <c r="B2392" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leonard t 
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
   fra </t>
         </is>
       </c>
-      <c r="C2392" t="n">
+      <c r="C2400" t="n">
         <v>101</v>
       </c>
     </row>
-    <row r="2393">
-      <c r="A2393" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2393" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2393" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2394">
-      <c r="A2394" t="inlineStr">
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B2394" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade du moustoir
-  lorient </t>
-        </is>
-      </c>
-      <c r="C2394" t="n">
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz riviera
+  nice </t>
+        </is>
+      </c>
+      <c r="C2401" t="n">
         <v>133</v>
       </c>
     </row>
-    <row r="2395">
-      <c r="A2395" t="inlineStr">
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B2395" t="inlineStr">
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade francis le ble
+  brest </t>
+        </is>
+      </c>
+      <c r="C2402" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="C2403" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade auguste delaune
+  reims </t>
+        </is>
+      </c>
+      <c r="C2404" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parc olympique lyonnais
+  lyon </t>
+        </is>
+      </c>
+      <c r="C2405" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">roazhon park
+  rennes </t>
+        </is>
+      </c>
+      <c r="C2406" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2407" t="inlineStr">
         <is>
           <t xml:space="preserve">stade pierre mauroy
   villeneuve d ascq </t>
         </is>
       </c>
-      <c r="C2395" t="n">
+      <c r="C2407" t="n">
         <v>133</v>
       </c>
     </row>
-    <row r="2396">
-      <c r="A2396" t="inlineStr">
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B2396" t="inlineStr">
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade geoffroy guichard
+  saint etienne </t>
+        </is>
+      </c>
+      <c r="C2408" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade velodrome
+  marseille </t>
+        </is>
+      </c>
+      <c r="C2409" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la meinau
+  strasbourg </t>
+        </is>
+      </c>
+      <c r="C2410" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la beaujoire
+  nantes </t>
+        </is>
+      </c>
+      <c r="C2411" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade raymond kopa
+  angers </t>
+        </is>
+      </c>
+      <c r="C2412" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadium municipal
+  toulouse </t>
+        </is>
+      </c>
+      <c r="C2413" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2414" t="inlineStr">
         <is>
           <t xml:space="preserve">stade louis ii
   monaco </t>
         </is>
       </c>
-      <c r="C2396" t="n">
+      <c r="C2414" t="n">
         <v>133</v>
       </c>
     </row>
-    <row r="2397">
-      <c r="A2397" t="inlineStr">
+    <row r="2415">
+      <c r="A2415" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B2397" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadium municipal
-  toulouse </t>
-        </is>
-      </c>
-      <c r="C2397" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2398">
-      <c r="A2398" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2398" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade saint symphorien
-  metz </t>
-        </is>
-      </c>
-      <c r="C2398" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2399">
-      <c r="A2399" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2399" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc olympique lyonnais
-  lyon </t>
-        </is>
-      </c>
-      <c r="C2399" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2400">
-      <c r="A2400" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2400" t="inlineStr">
+      <c r="B2415" t="inlineStr">
         <is>
           <t xml:space="preserve">stade oceane
   le havre </t>
         </is>
       </c>
-      <c r="C2400" t="n">
+      <c r="C2415" t="n">
         <v>133</v>
       </c>
     </row>
-    <row r="2401">
-      <c r="A2401" t="inlineStr">
+    <row r="2416">
+      <c r="A2416" t="inlineStr">
         <is>
           <t>venue</t>
         </is>
       </c>
-      <c r="B2401" t="inlineStr">
+      <c r="B2416" t="inlineStr">
         <is>
           <t xml:space="preserve">stade bollaert delelis
   lens </t>
         </is>
       </c>
-      <c r="C2401" t="n">
+      <c r="C2416" t="n">
         <v>133</v>
-      </c>
-    </row>
-    <row r="2402">
-      <c r="A2402" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2402" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade auguste delaune
-  reims </t>
-        </is>
-      </c>
-      <c r="C2402" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2403">
-      <c r="A2403" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B2403" t="inlineStr">
-        <is>
-          <t>pYaUUJs</t>
-        </is>
-      </c>
-      <c r="C2403" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2404">
-      <c r="A2404" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B2404" t="inlineStr">
-        <is>
-          <t>KAwSWno</t>
-        </is>
-      </c>
-      <c r="C2404" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2405">
-      <c r="A2405" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B2405" t="inlineStr">
-        <is>
-          <t>CWxpUrt</t>
-        </is>
-      </c>
-      <c r="C2405" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2406">
-      <c r="A2406" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B2406" t="inlineStr">
-        <is>
-          <t>UapruDa</t>
-        </is>
-      </c>
-      <c r="C2406" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2407">
-      <c r="A2407" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B2407" t="inlineStr">
-        <is>
-          <t>KYsw3uK</t>
-        </is>
-      </c>
-      <c r="C2407" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2408">
-      <c r="A2408" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B2408" t="inlineStr">
-        <is>
-          <t>YHU1oFV</t>
-        </is>
-      </c>
-      <c r="C2408" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2409">
-      <c r="A2409" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B2409" t="inlineStr">
-        <is>
-          <t>25Wk0Fk</t>
-        </is>
-      </c>
-      <c r="C2409" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2410">
-      <c r="A2410" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B2410" t="inlineStr">
-        <is>
-          <t>d0X3cO3</t>
-        </is>
-      </c>
-      <c r="C2410" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2411">
-      <c r="A2411" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B2411" t="inlineStr">
-        <is>
-          <t>SIFtcwD</t>
-        </is>
-      </c>
-      <c r="C2411" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2412">
-      <c r="A2412" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B2412" t="inlineStr">
-        <is>
-          <t>OYUbATy</t>
-        </is>
-      </c>
-      <c r="C2412" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="2413">
-      <c r="A2413" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B2413" t="inlineStr">
-        <is>
-          <t>zuUcoUw</t>
-        </is>
-      </c>
-      <c r="C2413" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="2414">
-      <c r="A2414" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B2414" t="inlineStr">
-        <is>
-          <t>YTLwacK</t>
-        </is>
-      </c>
-      <c r="C2414" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="2415">
-      <c r="A2415" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B2415" t="inlineStr">
-        <is>
-          <t>0tIbS51</t>
-        </is>
-      </c>
-      <c r="C2415" t="n">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="2416">
-      <c r="A2416" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B2416" t="inlineStr">
-        <is>
-          <t>8MdrBIU</t>
-        </is>
-      </c>
-      <c r="C2416" t="n">
-        <v>259</v>
       </c>
     </row>
     <row r="2417">
       <c r="A2417" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>venue</t>
         </is>
       </c>
       <c r="B2417" t="inlineStr">
         <is>
-          <t>AaLVdEG</t>
+          <t xml:space="preserve">parc des princes
+  paris </t>
         </is>
       </c>
       <c r="C2417" t="n">
-        <v>259</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2418">
       <c r="A2418" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>venue</t>
         </is>
       </c>
       <c r="B2418" t="inlineStr">
         <is>
-          <t>EgvyJSJ</t>
+          <t xml:space="preserve">stade de l abbe deschamps
+  auxerre </t>
         </is>
       </c>
       <c r="C2418" t="n">
-        <v>259</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2419">
@@ -36726,11 +36744,11 @@
       </c>
       <c r="B2419" t="inlineStr">
         <is>
-          <t>vVQcGxl</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="C2419" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2420">
@@ -36741,486 +36759,26 @@
       </c>
       <c r="B2420" t="inlineStr">
         <is>
-          <t>pCcFFE7</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="C2420" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2421">
       <c r="A2421" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_away</t>
         </is>
       </c>
       <c r="B2421" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
-  fra </t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="C2421" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2422">
-      <c r="A2422" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2422" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brisard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2422" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2423">
-      <c r="A2423" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2423" t="inlineStr">
-        <is>
-          <t xml:space="preserve">letexier f 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2423" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2424">
-      <c r="A2424" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2424" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade raymond kopa
-  angers </t>
-        </is>
-      </c>
-      <c r="C2424" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2425">
-      <c r="A2425" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2425" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la mosson
-  montpellier </t>
-        </is>
-      </c>
-      <c r="C2425" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2426">
-      <c r="A2426" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2426" t="inlineStr">
-        <is>
-          <t xml:space="preserve">roazhon park
-  rennes </t>
-        </is>
-      </c>
-      <c r="C2426" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2427">
-      <c r="A2427" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2427" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de l abbe deschamps
-  auxerre </t>
-        </is>
-      </c>
-      <c r="C2427" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2428">
-      <c r="A2428" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2428" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade francis le ble
-  brest </t>
-        </is>
-      </c>
-      <c r="C2428" t="n">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="2429">
-      <c r="A2429" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2429" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rainville n 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2429" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2430">
-      <c r="A2430" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2430" t="inlineStr">
-        <is>
-          <t xml:space="preserve">batta f 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2430" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2431">
-      <c r="A2431" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2431" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la beaujoire
-  nantes </t>
-        </is>
-      </c>
-      <c r="C2431" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2432">
-      <c r="A2432" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2432" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade de la meinau
-  strasbourg </t>
-        </is>
-      </c>
-      <c r="C2432" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2433">
-      <c r="A2433" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2433" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade velodrome
-  marseille </t>
-        </is>
-      </c>
-      <c r="C2433" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2434">
-      <c r="A2434" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2434" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz riviera
-  nice </t>
-        </is>
-      </c>
-      <c r="C2434" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2435">
-      <c r="A2435" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2435" t="inlineStr">
-        <is>
-          <t xml:space="preserve">parc des princes
-  paris </t>
-        </is>
-      </c>
-      <c r="C2435" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2436">
-      <c r="A2436" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="B2436" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stade geoffroy guichard
-  saint etienne </t>
-        </is>
-      </c>
-      <c r="C2436" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="2437">
-      <c r="A2437" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2437" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2437" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2438">
-      <c r="A2438" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2438" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2438" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2439">
-      <c r="A2439" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2439" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2439" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2440">
-      <c r="A2440" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2440" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2440" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2441">
-      <c r="A2441" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B2441" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="C2441" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2442">
-      <c r="A2442" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B2442" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="C2442" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2443">
-      <c r="A2443" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B2443" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="C2443" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2444">
-      <c r="A2444" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="B2444" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="C2444" t="n">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2445">
-      <c r="A2445" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2445" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kherradji a 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2445" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2446">
-      <c r="A2446" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2446" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frappart s 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2446" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2447">
-      <c r="A2447" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2447" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2447" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2448">
-      <c r="A2448" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2448" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dechepy b 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2448" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="2449">
-      <c r="A2449" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="B2449" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="C2449" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="2450">
-      <c r="A2450" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="B2450" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="C2450" t="n">
-        <v>314</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>

--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2421"/>
+  <dimension ref="A1:C2428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36781,6 +36781,118 @@
         <v>258</v>
       </c>
     </row>
+    <row r="2422">
+      <c r="A2422" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2422" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2423" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2424" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2425" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2426" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2427" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2428" t="n">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2428"/>
+  <dimension ref="A1:C2433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36893,6 +36893,84 @@
         <v>102</v>
       </c>
     </row>
+    <row r="2429">
+      <c r="A2429" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2429" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2430" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B2431" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="C2431" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B2432" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="C2432" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B2433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="C2433" t="n">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2433"/>
+  <dimension ref="A1:C2434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36971,6 +36971,22 @@
         <v>104</v>
       </c>
     </row>
+    <row r="2434">
+      <c r="A2434" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B2434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stade de la mosson
+  montpellier </t>
+        </is>
+      </c>
+      <c r="C2434" t="n">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/france/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2434"/>
+  <dimension ref="A1:C2436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36987,6 +36987,36 @@
         <v>134</v>
       </c>
     </row>
+    <row r="2435">
+      <c r="A2435" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B2435" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="C2435" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B2436" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="C2436" t="n">
+        <v>313</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
